--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -171,28 +171,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>TEMAS DE CIENCIAS DE LA SALUD</t>
-  </si>
-  <si>
-    <t>TEMAS DE FÍSICA</t>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
     <t>NC</t>
@@ -903,7 +897,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -957,7 +951,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -980,7 +974,7 @@
         <v>7</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -1034,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1057,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -1111,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1134,7 +1128,7 @@
         <v>7</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1188,7 +1182,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1211,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -1265,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1288,7 +1282,7 @@
         <v>10</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -1342,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1365,7 +1359,7 @@
         <v>6</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -1419,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1442,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>8</v>
@@ -1496,7 +1490,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1519,7 +1513,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -1573,7 +1567,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1596,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G13">
         <v>7</v>
@@ -1650,7 +1644,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1673,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1727,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1750,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -1804,7 +1798,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1827,7 +1821,7 @@
         <v>8</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>8</v>
@@ -1881,7 +1875,7 @@
         <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1904,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -1958,7 +1952,7 @@
         <v>10</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1981,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>7</v>
@@ -2035,7 +2029,7 @@
         <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2058,7 +2052,7 @@
         <v>9</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>8</v>
@@ -2112,7 +2106,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -2135,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>8</v>
@@ -2189,7 +2183,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2212,7 +2206,7 @@
         <v>9</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <v>6</v>
@@ -2266,7 +2260,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2289,7 +2283,7 @@
         <v>8</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2343,7 +2337,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2366,7 +2360,7 @@
         <v>8</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>6</v>
@@ -2420,7 +2414,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2443,7 +2437,7 @@
         <v>9</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G24">
         <v>7</v>
@@ -2497,7 +2491,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2520,7 +2514,7 @@
         <v>6</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2574,7 +2568,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2597,7 +2591,7 @@
         <v>5</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>4</v>
@@ -2651,7 +2645,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2674,7 +2668,7 @@
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2728,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2751,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -2805,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2828,7 +2822,7 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>7</v>
@@ -2882,7 +2876,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -3015,7 +3009,7 @@
         <v>120</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>64</v>
@@ -3074,7 +3068,7 @@
         <v>120</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
         <v>96</v>
@@ -3133,7 +3127,7 @@
         <v>120</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -3192,7 +3186,7 @@
         <v>120</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>84</v>
@@ -3251,7 +3245,7 @@
         <v>120</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>96</v>
@@ -3310,7 +3304,7 @@
         <v>120</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>96</v>
@@ -3369,7 +3363,7 @@
         <v>120</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
         <v>92</v>
@@ -3428,7 +3422,7 @@
         <v>120</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
@@ -3487,7 +3481,7 @@
         <v>120</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -3546,7 +3540,7 @@
         <v>120</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>100</v>
@@ -3605,7 +3599,7 @@
         <v>120</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>92</v>
@@ -3664,7 +3658,7 @@
         <v>120</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>96</v>
@@ -3723,7 +3717,7 @@
         <v>120</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -3782,7 +3776,7 @@
         <v>120</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>92</v>
@@ -3841,7 +3835,7 @@
         <v>120</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>100</v>
@@ -3900,7 +3894,7 @@
         <v>120</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>100</v>
@@ -3959,7 +3953,7 @@
         <v>120</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -4018,7 +4012,7 @@
         <v>120</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>100</v>
@@ -4077,7 +4071,7 @@
         <v>120</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>100</v>
@@ -4136,7 +4130,7 @@
         <v>120</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -4195,7 +4189,7 @@
         <v>120</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>100</v>
@@ -4254,7 +4248,7 @@
         <v>120</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>100</v>
@@ -4313,7 +4307,7 @@
         <v>120</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>84</v>
@@ -4372,7 +4366,7 @@
         <v>120</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -4431,7 +4425,7 @@
         <v>120</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>96</v>
@@ -4490,7 +4484,7 @@
         <v>120</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>84</v>
@@ -4544,7 +4538,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
@@ -4584,13 +4578,13 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -4598,112 +4592,139 @@
       <c r="E2">
         <v>0</v>
       </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="I2">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="J2">
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
       <c r="C3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>65.38</v>
+      </c>
+      <c r="G3">
+        <v>34.62</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>76.92</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>23.08</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>11.54</v>
+      </c>
+      <c r="H5">
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>65.38</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G6">
-        <v>34.62</v>
+        <v>3.85</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4714,97 +4735,33 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>26</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>76.92</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="G7">
-        <v>23.08</v>
+        <v>3.85</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>88.45999999999999</v>
-      </c>
-      <c r="G8">
-        <v>11.54</v>
-      </c>
-      <c r="H8">
-        <v>7.6</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>25</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="G9">
-        <v>3.85</v>
-      </c>
-      <c r="H9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
         <v>0</v>
       </c>
     </row>
@@ -4815,7 +4772,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4824,16 +4781,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4847,70 +4804,70 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
         <v>104</v>
@@ -4919,967 +4876,447 @@
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920192</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
         <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920192</v>
+        <v>20330051920197</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920193</v>
+        <v>20330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>20330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920196</v>
+        <v>20330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920196</v>
+        <v>20330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920197</v>
+        <v>19330051920280</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920197</v>
+        <v>20330051920202</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920198</v>
+        <v>20330051920204</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920198</v>
+        <v>20330051920206</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920199</v>
+        <v>19330051920290</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920199</v>
+        <v>20330051920209</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920200</v>
+        <v>20330051920210</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920200</v>
+        <v>20330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920201</v>
+        <v>20330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920201</v>
+        <v>20330051920214</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920280</v>
+        <v>20330051920215</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920280</v>
+        <v>19330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920202</v>
+        <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920202</v>
+        <v>20330051920218</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
         <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920204</v>
+        <v>20330051920219</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920204</v>
+        <v>20330051920259</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920206</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920206</v>
-      </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920290</v>
-      </c>
-      <c r="B30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920290</v>
-      </c>
-      <c r="B31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920209</v>
-      </c>
-      <c r="B32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920209</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>95</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920210</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920210</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" t="s">
-        <v>119</v>
-      </c>
-      <c r="E35" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920212</v>
-      </c>
-      <c r="B36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" t="s">
-        <v>96</v>
-      </c>
-      <c r="D36" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920212</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" t="s">
-        <v>96</v>
-      </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920213</v>
-      </c>
-      <c r="B38" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920213</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>97</v>
-      </c>
-      <c r="D39" t="s">
-        <v>121</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920214</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920214</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" t="s">
-        <v>122</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920215</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920215</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920177</v>
-      </c>
-      <c r="B44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" t="s">
-        <v>124</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920177</v>
-      </c>
-      <c r="B45" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" t="s">
-        <v>100</v>
-      </c>
-      <c r="D45" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920217</v>
-      </c>
-      <c r="B46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920217</v>
-      </c>
-      <c r="B47" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" t="s">
-        <v>101</v>
-      </c>
-      <c r="D47" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920218</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>96</v>
-      </c>
-      <c r="D48" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920218</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" t="s">
-        <v>126</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920219</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920219</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>102</v>
-      </c>
-      <c r="D51" t="s">
-        <v>127</v>
-      </c>
-      <c r="E51" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920259</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D52" t="s">
-        <v>128</v>
-      </c>
-      <c r="E52" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920259</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>83</v>
-      </c>
-      <c r="D53" t="s">
-        <v>128</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5898,16 +5335,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>48</v>
@@ -5918,16 +5355,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5935,16 +5372,16 @@
         <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5952,16 +5389,16 @@
         <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5969,16 +5406,16 @@
         <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5986,16 +5423,16 @@
         <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -6003,16 +5440,16 @@
         <v>20330051920197</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -6020,16 +5457,16 @@
         <v>20330051920198</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -6037,16 +5474,16 @@
         <v>20330051920199</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6054,16 +5491,16 @@
         <v>20330051920200</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -6071,16 +5508,16 @@
         <v>20330051920201</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6088,16 +5525,16 @@
         <v>19330051920280</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -6105,16 +5542,16 @@
         <v>20330051920202</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6122,16 +5559,16 @@
         <v>20330051920204</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -6139,16 +5576,16 @@
         <v>20330051920206</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -6156,16 +5593,16 @@
         <v>19330051920290</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6173,16 +5610,16 @@
         <v>20330051920209</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6190,16 +5627,16 @@
         <v>20330051920210</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -6207,16 +5644,16 @@
         <v>20330051920212</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -6224,16 +5661,16 @@
         <v>20330051920213</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -6241,16 +5678,16 @@
         <v>20330051920214</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -6258,16 +5695,16 @@
         <v>20330051920215</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -6275,16 +5712,16 @@
         <v>19330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -6292,16 +5729,16 @@
         <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -6309,16 +5746,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -6326,16 +5763,16 @@
         <v>20330051920219</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -6343,16 +5780,16 @@
         <v>20330051920259</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6362,7 +5799,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6371,16 +5808,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6394,22 +5831,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920197</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6417,45 +5854,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920197</v>
+        <v>20330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920198</v>
+        <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -6463,45 +5900,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920198</v>
+        <v>20330051920192</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920199</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6509,45 +5946,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920199</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920201</v>
+        <v>20330051920200</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6555,45 +5992,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920201</v>
+        <v>20330051920200</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -6601,45 +6038,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920204</v>
+        <v>20330051920217</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6647,45 +6084,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920204</v>
+        <v>20330051920217</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920206</v>
+        <v>20330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -6693,45 +6130,45 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920206</v>
+        <v>20330051920218</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920290</v>
+        <v>20330051920219</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -6739,45 +6176,45 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920290</v>
+        <v>20330051920219</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920209</v>
+        <v>20330051920197</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -6785,22 +6222,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920209</v>
+        <v>20330051920198</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -6808,22 +6245,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920210</v>
+        <v>20330051920199</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -6831,22 +6268,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920210</v>
+        <v>20330051920201</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -6854,22 +6291,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920212</v>
+        <v>19330051920280</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -6877,22 +6314,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920212</v>
+        <v>20330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -6900,22 +6337,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920213</v>
+        <v>20330051920206</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -6923,22 +6360,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920213</v>
+        <v>19330051920290</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G25">
         <v>-1</v>
@@ -6946,22 +6383,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920215</v>
+        <v>20330051920209</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -6969,22 +6406,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920215</v>
+        <v>20330051920210</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -6992,22 +6429,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920259</v>
+        <v>20330051920212</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -7015,24 +6452,70 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
+        <v>20330051920213</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920215</v>
+      </c>
+      <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
         <v>20330051920259</v>
       </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>83</v>
-      </c>
-      <c r="D29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29">
+      <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>50</v>
+      </c>
+      <c r="G31">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="127">
   <si>
     <t>Materia</t>
   </si>
@@ -171,13 +171,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
     <t>Domínguez Burgos Marioscar</t>
@@ -885,7 +885,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -939,7 +939,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1016,7 +1016,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1039,7 +1039,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1116,7 +1116,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -1170,7 +1170,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1193,7 +1193,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>10</v>
@@ -1247,7 +1247,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1270,7 +1270,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -1324,7 +1324,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1347,7 +1347,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1401,7 +1401,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1424,7 +1424,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>10</v>
@@ -1478,7 +1478,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1501,7 +1501,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1555,7 +1555,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1578,7 +1578,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>10</v>
@@ -1632,7 +1632,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1655,7 +1655,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1732,7 +1732,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1786,7 +1786,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1809,7 +1809,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>8</v>
@@ -1863,7 +1863,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1886,7 +1886,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -1940,7 +1940,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1963,7 +1963,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>10</v>
@@ -2017,7 +2017,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>10</v>
@@ -2040,7 +2040,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2117,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -2171,7 +2171,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2194,7 +2194,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C21">
         <v>8</v>
@@ -2248,7 +2248,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2271,7 +2271,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>10</v>
@@ -2325,7 +2325,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>10</v>
@@ -2348,7 +2348,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>9</v>
@@ -2402,7 +2402,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2425,7 +2425,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2479,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2502,7 +2502,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -2556,7 +2556,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2579,7 +2579,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C26">
         <v>8</v>
@@ -2633,7 +2633,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2656,7 +2656,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>9</v>
@@ -2710,7 +2710,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2733,7 +2733,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -2787,7 +2787,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>10</v>
@@ -2810,7 +2810,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -2864,7 +2864,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -2997,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -3056,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3115,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>95</v>
@@ -3174,7 +3174,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3233,7 +3233,7 @@
         <v>16</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3292,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -3351,7 +3351,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>95</v>
@@ -3410,7 +3410,7 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3469,7 +3469,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>90</v>
@@ -3528,7 +3528,7 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -3587,7 +3587,7 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -3646,7 +3646,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -3705,7 +3705,7 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -3764,7 +3764,7 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -3823,7 +3823,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3882,7 +3882,7 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3941,7 +3941,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -4000,7 +4000,7 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -4059,7 +4059,7 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -4118,7 +4118,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -4177,7 +4177,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -4236,7 +4236,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -4295,7 +4295,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -4354,7 +4354,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>95</v>
@@ -4413,7 +4413,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -4472,7 +4472,7 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>95</v>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>50</v>
@@ -4587,27 +4587,30 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>65.38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>34.62</v>
+      </c>
+      <c r="H2">
+        <v>6.5</v>
       </c>
       <c r="I2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -4616,19 +4619,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>65.38</v>
+        <v>76.92</v>
       </c>
       <c r="G3">
-        <v>34.62</v>
+        <v>23.08</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4639,7 +4642,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4660,7 +4663,7 @@
         <v>23.08</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4772,7 +4775,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4797,526 +4800,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920191</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920193</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920196</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920197</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920198</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920199</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920200</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920280</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920202</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920204</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920206</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920290</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920209</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920210</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920212</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920213</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920214</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920215</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920217</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920218</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920219</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920259</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5364,7 +4847,7 @@
         <v>101</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5381,7 +4864,7 @@
         <v>102</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5398,7 +4881,7 @@
         <v>103</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5415,7 +4898,7 @@
         <v>104</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5432,7 +4915,7 @@
         <v>105</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5449,7 +4932,7 @@
         <v>106</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5466,7 +4949,7 @@
         <v>107</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5483,7 +4966,7 @@
         <v>108</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5500,7 +4983,7 @@
         <v>109</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5517,7 +5000,7 @@
         <v>110</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5534,7 +5017,7 @@
         <v>111</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5551,7 +5034,7 @@
         <v>112</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5568,7 +5051,7 @@
         <v>113</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5585,7 +5068,7 @@
         <v>114</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5602,7 +5085,7 @@
         <v>115</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -5619,7 +5102,7 @@
         <v>116</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5636,7 +5119,7 @@
         <v>117</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5653,7 +5136,7 @@
         <v>118</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -5670,7 +5153,7 @@
         <v>119</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5687,7 +5170,7 @@
         <v>120</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5704,7 +5187,7 @@
         <v>121</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5721,7 +5204,7 @@
         <v>122</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5738,7 +5221,7 @@
         <v>123</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5755,7 +5238,7 @@
         <v>124</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5772,7 +5255,7 @@
         <v>125</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5789,7 +5272,7 @@
         <v>126</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5799,7 +5282,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5846,10 +5329,10 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5869,7 +5352,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5877,45 +5360,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920192</v>
+        <v>20330051920196</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920192</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5923,45 +5406,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5969,25 +5452,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920200</v>
+        <v>20330051920192</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -6027,33 +5510,33 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>50</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920202</v>
+        <v>20330051920210</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
         <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -6073,33 +5556,33 @@
         <v>123</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
         <v>50</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920217</v>
+        <v>20330051920218</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6107,416 +5590,48 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920218</v>
+        <v>20330051920219</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
         <v>50</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920218</v>
+        <v>20330051920259</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920219</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920219</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920197</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920198</v>
-      </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920199</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920201</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920280</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920204</v>
-      </c>
-      <c r="B23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920206</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920290</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>20330051920209</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920210</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920212</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>50</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920213</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" t="s">
-        <v>119</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>20330051920215</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>50</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>20330051920259</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>50</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -186,7 +186,7 @@
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Mateos Sanchez Jorge</t>
   </si>
   <si>
     <t>NC</t>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -204,199 +203,49 @@
     <t>ASCENCION</t>
   </si>
   <si>
-    <t>ARIAS</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
-    <t>ANALI</t>
+    <t>ALEJANDRA</t>
   </si>
   <si>
     <t>JOCELYN</t>
   </si>
   <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
     <t>JULIO CESAR</t>
   </si>
   <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
     <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>EMILY</t>
   </si>
   <si>
     <t>JESUS URIEL</t>
@@ -406,6 +255,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -458,11 +310,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,10 +759,10 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -918,7 +771,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -983,10 +836,10 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -995,7 +848,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1060,10 +913,10 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1072,7 +925,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1137,10 +990,10 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1149,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1214,10 +1067,10 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1226,7 +1079,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1253,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1291,10 +1144,10 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1303,7 +1156,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1327,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1339,7 +1192,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1368,10 +1221,10 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1380,7 +1233,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1404,7 +1257,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>6</v>
@@ -1416,7 +1269,7 @@
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1445,10 +1298,10 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1457,7 +1310,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1484,7 +1337,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1493,7 +1346,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1522,10 +1375,10 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1534,7 +1387,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1558,10 +1411,10 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1599,10 +1452,10 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1611,7 +1464,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1676,10 +1529,10 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1688,7 +1541,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1753,10 +1606,10 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1765,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1792,7 +1645,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1801,7 +1654,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1830,10 +1683,10 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1842,7 +1695,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1866,7 +1719,7 @@
         <v>8</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>6</v>
@@ -1907,10 +1760,10 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1919,7 +1772,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1946,7 +1799,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -1984,10 +1837,10 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1996,7 +1849,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2061,10 +1914,10 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2073,7 +1926,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2138,10 +1991,10 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2150,7 +2003,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2174,10 +2027,10 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2186,7 +2039,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2215,10 +2068,10 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2227,7 +2080,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2251,10 +2104,10 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2292,10 +2145,10 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2304,7 +2157,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2331,7 +2184,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2340,7 +2193,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2369,10 +2222,10 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2381,7 +2234,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2405,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2417,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2446,10 +2299,10 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2458,7 +2311,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2523,10 +2376,10 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2535,7 +2388,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2559,7 +2412,7 @@
         <v>7</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2600,10 +2453,10 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2612,7 +2465,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2636,7 +2489,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2677,10 +2530,10 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2689,7 +2542,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2754,10 +2607,10 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2766,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2802,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2831,10 +2684,10 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2843,7 +2696,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2867,10 +2720,10 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2879,7 +2732,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3077,10 +2930,10 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -3089,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -3136,10 +2989,10 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -3148,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -3195,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -3207,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -3254,10 +3107,10 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3266,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -3313,10 +3166,10 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -3325,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -3372,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3384,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -3431,10 +3284,10 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -3443,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -3490,10 +3343,10 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -3502,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -3549,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -3561,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3608,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -3620,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3667,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3679,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3726,10 +3579,10 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3738,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3785,10 +3638,10 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3797,7 +3650,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3844,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -3856,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -3903,10 +3756,10 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3915,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -3962,10 +3815,10 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3974,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4021,10 +3874,10 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -4033,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -4080,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -4092,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -4139,10 +3992,10 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -4151,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -4198,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4210,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -4257,10 +4110,10 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4269,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -4316,10 +4169,10 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -4328,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -4375,10 +4228,10 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4387,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -4434,10 +4287,10 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4446,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -4493,10 +4346,10 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -4505,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -4542,6 +4395,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4587,24 +4442,24 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>9</v>
-      </c>
-      <c r="F2">
-        <v>65.38</v>
-      </c>
-      <c r="G2">
-        <v>34.62</v>
+        <v>8</v>
+      </c>
+      <c r="F2" s="2">
+        <v>69.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>30.8</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4619,16 +4474,16 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>76.92</v>
-      </c>
-      <c r="G3">
-        <v>23.08</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>69.2</v>
+      </c>
+      <c r="G3" s="2">
+        <v>30.8</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -4636,7 +4491,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4656,11 +4511,11 @@
       <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4">
-        <v>76.92</v>
-      </c>
-      <c r="G4">
-        <v>23.08</v>
+      <c r="F4" s="2">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>23.1</v>
       </c>
       <c r="H4">
         <v>7.5</v>
@@ -4668,7 +4523,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4688,11 +4543,11 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>88.45999999999999</v>
-      </c>
-      <c r="G5">
-        <v>11.54</v>
+      <c r="F5" s="2">
+        <v>88.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>11.5</v>
       </c>
       <c r="H5">
         <v>7.6</v>
@@ -4700,7 +4555,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4720,11 +4575,11 @@
       <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="G6">
-        <v>3.85</v>
+      <c r="F6" s="2">
+        <v>96.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3.8</v>
       </c>
       <c r="H6">
         <v>9.1</v>
@@ -4732,7 +4587,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4752,19 +4607,19 @@
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>96.15000000000001</v>
-      </c>
-      <c r="G7">
-        <v>3.85</v>
+      <c r="F7" s="2">
+        <v>96.2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.8</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -4809,480 +4664,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920190</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920191</v>
-      </c>
-      <c r="B3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920192</v>
-      </c>
-      <c r="B4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920193</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920196</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920197</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920198</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920199</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920200</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920201</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>19330051920280</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920202</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920204</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920206</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>19330051920290</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920209</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>20330051920210</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920212</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920213</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>20330051920214</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>20330051920215</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" t="s">
-        <v>121</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>19330051920177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>20330051920217</v>
-      </c>
-      <c r="B24" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>20330051920218</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>20330051920219</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>20330051920259</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5320,10 +4702,10 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5343,10 +4725,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5360,22 +4742,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5383,16 +4765,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5406,16 +4788,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>20330051920192</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5429,16 +4811,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>20330051920202</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5452,22 +4834,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920192</v>
+        <v>20330051920210</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5475,22 +4857,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920200</v>
+        <v>20330051920217</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5498,139 +4880,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920202</v>
+        <v>20330051920259</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920210</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920217</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920218</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920219</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920259</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
   <si>
     <t>Materia</t>
   </si>
@@ -212,9 +212,6 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -240,9 +237,6 @@
   </si>
   <si>
     <t>ITZEL</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>LUIS DIEGO</t>
@@ -756,7 +750,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -768,7 +762,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -833,7 +827,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -845,7 +839,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -881,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -910,7 +904,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -922,7 +916,7 @@
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -987,7 +981,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>10</v>
@@ -999,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1035,7 +1029,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1064,7 +1058,7 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>10</v>
@@ -1076,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1100,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1112,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1141,7 +1135,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -1153,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>9</v>
@@ -1189,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1218,7 +1212,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>6</v>
@@ -1230,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -1266,7 +1260,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1295,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -1307,7 +1301,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>9</v>
@@ -1372,7 +1366,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1384,7 +1378,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>5</v>
@@ -1449,7 +1443,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -1461,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1485,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1526,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1538,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>7</v>
@@ -1562,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1603,7 +1597,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1615,7 +1609,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>4</v>
@@ -1639,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1651,7 +1645,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -1680,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>10</v>
@@ -1692,7 +1686,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1716,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1757,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -1769,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -1793,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -1834,7 +1828,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -1846,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -1911,7 +1905,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -1923,7 +1917,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -1988,7 +1982,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2000,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -2024,7 +2018,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2036,7 +2030,7 @@
         <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2065,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>10</v>
@@ -2077,7 +2071,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -2101,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2113,7 +2107,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2142,7 +2136,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>10</v>
@@ -2154,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>8</v>
@@ -2219,7 +2213,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>10</v>
@@ -2231,7 +2225,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>7</v>
@@ -2267,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2296,7 +2290,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2308,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2373,7 +2367,7 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2385,7 +2379,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2450,7 +2444,7 @@
         <v>4</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -2462,7 +2456,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>6</v>
@@ -2498,7 +2492,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2527,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>8</v>
@@ -2539,7 +2533,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2563,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>9</v>
@@ -2575,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2604,7 +2598,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2616,7 +2610,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -2652,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2681,7 +2675,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>8</v>
@@ -2693,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2717,7 +2711,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2729,7 +2723,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -2880,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2927,7 +2921,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2939,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>116</v>
@@ -2986,7 +2980,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>95</v>
@@ -2998,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>108</v>
@@ -3045,7 +3039,7 @@
         <v>84</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3057,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3104,7 +3098,7 @@
         <v>96</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3116,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>120</v>
@@ -3163,7 +3157,7 @@
         <v>96</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -3175,7 +3169,7 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>104</v>
@@ -3222,7 +3216,7 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>95</v>
@@ -3234,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10">
         <v>104</v>
@@ -3281,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3293,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
         <v>116</v>
@@ -3340,7 +3334,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>90</v>
@@ -3352,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3399,7 +3393,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -3411,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13">
         <v>104</v>
@@ -3458,7 +3452,7 @@
         <v>92</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -3470,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14">
         <v>120</v>
@@ -3517,7 +3511,7 @@
         <v>96</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -3529,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>104</v>
@@ -3576,7 +3570,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3588,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16">
         <v>108</v>
@@ -3635,7 +3629,7 @@
         <v>92</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -3647,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>116</v>
@@ -3694,7 +3688,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3706,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
         <v>116</v>
@@ -3753,7 +3747,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -3765,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M19">
         <v>108</v>
@@ -3812,7 +3806,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -3824,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20">
         <v>112</v>
@@ -3871,7 +3865,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -3883,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>104</v>
@@ -3930,7 +3924,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>100</v>
@@ -3942,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22">
         <v>108</v>
@@ -3989,7 +3983,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4001,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
         <v>116</v>
@@ -4048,7 +4042,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4060,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>120</v>
@@ -4107,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -4119,7 +4113,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -4166,7 +4160,7 @@
         <v>84</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4178,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M26">
         <v>104</v>
@@ -4225,7 +4219,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4237,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27">
         <v>104</v>
@@ -4284,7 +4278,7 @@
         <v>96</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -4296,7 +4290,7 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -4343,7 +4337,7 @@
         <v>84</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>100</v>
@@ -4355,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29">
         <v>104</v>
@@ -4506,19 +4500,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>76.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4570,19 +4564,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="G6" s="2">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="H6">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4664,7 +4658,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4702,10 +4696,10 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4725,10 +4719,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4748,10 +4742,10 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4771,10 +4765,10 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4794,10 +4788,10 @@
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4817,10 +4811,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4834,22 +4828,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920210</v>
+        <v>20330051920217</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4857,47 +4851,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920217</v>
+        <v>20330051920259</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920259</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="78">
   <si>
     <t>Materia</t>
   </si>
@@ -176,12 +176,12 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -206,13 +206,16 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>DE LA TEJA</t>
   </si>
   <si>
     <t>CASTILLO</t>
@@ -221,10 +224,13 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>SOLIS</t>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>REYNA ARISBETH</t>
@@ -233,16 +239,19 @@
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
     <t>JOCELYN</t>
   </si>
   <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
+    <t>ALISSON FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -759,7 +768,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -836,7 +845,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -913,7 +922,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -990,7 +999,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1067,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>8</v>
@@ -1144,7 +1153,7 @@
         <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1221,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1257,7 +1266,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1298,7 +1307,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1375,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -1411,7 +1420,7 @@
         <v>5</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1452,7 +1461,7 @@
         <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>8</v>
@@ -1488,7 +1497,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1529,7 +1538,7 @@
         <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1606,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -1683,7 +1692,7 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1760,7 +1769,7 @@
         <v>8</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -1796,7 +1805,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -1837,7 +1846,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -1914,7 +1923,7 @@
         <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -1991,7 +2000,7 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2027,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2068,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2104,7 +2113,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2145,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>8</v>
@@ -2181,7 +2190,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2222,7 +2231,7 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -2299,7 +2308,7 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2376,7 +2385,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2453,7 +2462,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -2530,7 +2539,7 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -2566,7 +2575,7 @@
         <v>6</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2607,7 +2616,7 @@
         <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
         <v>8</v>
@@ -2684,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -2720,7 +2729,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>5</v>
@@ -2871,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -2930,7 +2939,7 @@
         <v>116</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -2989,7 +2998,7 @@
         <v>120</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3048,7 +3057,7 @@
         <v>116</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3107,7 +3116,7 @@
         <v>120</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3166,7 +3175,7 @@
         <v>112</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3225,7 +3234,7 @@
         <v>112</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3284,7 +3293,7 @@
         <v>120</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3343,7 +3352,7 @@
         <v>120</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -3402,7 +3411,7 @@
         <v>120</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3461,7 +3470,7 @@
         <v>120</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -3520,7 +3529,7 @@
         <v>112</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3579,7 +3588,7 @@
         <v>120</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3638,7 +3647,7 @@
         <v>120</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3697,7 +3706,7 @@
         <v>120</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -3756,7 +3765,7 @@
         <v>116</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -3815,7 +3824,7 @@
         <v>120</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -3874,7 +3883,7 @@
         <v>108</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -3933,7 +3942,7 @@
         <v>112</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -3992,7 +4001,7 @@
         <v>120</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4051,7 +4060,7 @@
         <v>120</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4110,7 +4119,7 @@
         <v>120</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4169,7 +4178,7 @@
         <v>120</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4228,7 +4237,7 @@
         <v>112</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4287,7 +4296,7 @@
         <v>120</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4346,7 +4355,7 @@
         <v>120</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4491,7 +4500,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4500,19 +4509,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>84.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>15.4</v>
+        <v>26.9</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4523,7 +4532,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4532,19 +4541,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>11.5</v>
+        <v>15.4</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4658,7 +4667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4696,16 +4705,16 @@
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4719,10 +4728,10 @@
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4742,10 +4751,10 @@
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4765,10 +4774,10 @@
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4782,22 +4791,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920192</v>
+        <v>20330051920217</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4805,16 +4814,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920202</v>
+        <v>20330051920217</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4828,22 +4837,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920217</v>
+        <v>20330051920259</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4854,10 +4863,10 @@
         <v>20330051920259</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
@@ -4869,6 +4878,75 @@
         <v>54</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920192</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920202</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920218</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -2871,40 +2871,40 @@
         <v>64</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>63.6</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>29.1</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>63.6</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2918,10 +2918,10 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>104</v>
+        <v>86.7</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -2936,7 +2936,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>116</v>
+        <v>91.7</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -2945,25 +2945,25 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>116</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2977,10 +2977,10 @@
         <v>95</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -2995,7 +2995,7 @@
         <v>95</v>
       </c>
       <c r="J6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3004,25 +3004,25 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3036,10 +3036,10 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3054,7 +3054,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -3063,25 +3063,25 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3095,10 +3095,10 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3113,7 +3113,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -3122,25 +3122,25 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3154,10 +3154,10 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>104</v>
+        <v>86.7</v>
       </c>
       <c r="E9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -3172,7 +3172,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3181,25 +3181,25 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>104</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3213,10 +3213,10 @@
         <v>95</v>
       </c>
       <c r="D10">
-        <v>104</v>
+        <v>86.7</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3231,7 +3231,7 @@
         <v>95</v>
       </c>
       <c r="J10">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -3240,25 +3240,25 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>104</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3272,10 +3272,10 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3290,7 +3290,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -3299,25 +3299,25 @@
         <v>100</v>
       </c>
       <c r="M11">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3331,10 +3331,10 @@
         <v>90</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3349,34 +3349,34 @@
         <v>90</v>
       </c>
       <c r="J12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>72</v>
+        <v>87.3</v>
       </c>
       <c r="L12">
         <v>100</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3390,10 +3390,10 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3408,7 +3408,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -3417,25 +3417,25 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3449,10 +3449,10 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -3467,7 +3467,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -3476,25 +3476,25 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3508,10 +3508,10 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3526,34 +3526,34 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="K15">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>104</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3567,10 +3567,10 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -3585,7 +3585,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -3594,25 +3594,25 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3626,10 +3626,10 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="E17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -3644,7 +3644,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>120</v>
+        <v>96.7</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3653,25 +3653,25 @@
         <v>100</v>
       </c>
       <c r="M17">
-        <v>116</v>
+        <v>94.5</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3685,10 +3685,10 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -3703,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -3712,25 +3712,25 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3744,10 +3744,10 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -3762,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -3771,25 +3771,25 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3803,10 +3803,10 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -3821,7 +3821,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -3830,25 +3830,25 @@
         <v>100</v>
       </c>
       <c r="M20">
-        <v>112</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3862,10 +3862,10 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -3880,7 +3880,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -3889,25 +3889,25 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3921,10 +3921,10 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="E22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -3939,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -3948,25 +3948,25 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>108</v>
+        <v>94.5</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -3980,10 +3980,10 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -3998,7 +3998,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -4007,25 +4007,25 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>116</v>
+        <v>98.2</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4039,10 +4039,10 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4057,7 +4057,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -4066,25 +4066,25 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4098,10 +4098,10 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4116,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -4125,25 +4125,25 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4157,10 +4157,10 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="E26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4175,7 +4175,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>120</v>
+        <v>98.3</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -4184,25 +4184,25 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>104</v>
+        <v>85.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4216,10 +4216,10 @@
         <v>95</v>
       </c>
       <c r="D27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4231,10 +4231,10 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J27">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -4243,25 +4243,25 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>104</v>
+        <v>92.7</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4275,10 +4275,10 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4293,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -4302,25 +4302,25 @@
         <v>100</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>98.2</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4334,10 +4334,10 @@
         <v>95</v>
       </c>
       <c r="D29">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="E29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4349,10 +4349,10 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>98.3</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -4361,25 +4361,25 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>104</v>
+        <v>85.5</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>85.5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ALCV - Estadisticos 20222.xlsx
+++ b/grupos/6ALCV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="74">
   <si>
     <t>Materia</t>
   </si>
@@ -176,18 +176,18 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Mateos Sanchez Jorge</t>
+  </si>
+  <si>
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Mateos Sanchez Jorge</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -200,22 +200,25 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ASCENCION</t>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>CASTILLO</t>
@@ -224,34 +227,19 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -777,22 +765,22 @@
         <v>4</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -854,34 +842,34 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -931,34 +919,34 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>9</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1008,40 +996,40 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1085,22 +1073,22 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1109,7 +1097,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1118,7 +1106,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1162,31 +1150,31 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1239,40 +1227,40 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>7</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1316,22 +1304,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1393,34 +1381,34 @@
         <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1470,28 +1458,28 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>8</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1547,22 +1535,22 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1571,7 +1559,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1624,34 +1612,34 @@
         <v>4</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1701,22 +1689,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1725,16 +1713,16 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1778,22 +1766,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1802,7 +1790,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -1855,22 +1843,22 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1932,28 +1920,28 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2009,40 +1997,40 @@
         <v>4</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>8</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2086,31 +2074,31 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2163,22 +2151,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2187,16 +2175,16 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2240,22 +2228,22 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2267,7 +2255,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2317,22 +2305,22 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2341,10 +2329,10 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2394,25 +2382,25 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>8</v>
@@ -2424,10 +2412,10 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2471,40 +2459,40 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2548,40 +2536,40 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>6</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2625,22 +2613,22 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2649,7 +2637,7 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2702,40 +2690,40 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2889,22 +2877,22 @@
         <v>29.1</v>
       </c>
       <c r="N4">
+        <v>27.3</v>
+      </c>
+      <c r="O4">
+        <v>1.7</v>
+      </c>
+      <c r="P4">
+        <v>3.3</v>
+      </c>
+      <c r="Q4">
         <v>43.8</v>
       </c>
-      <c r="O4">
-        <v>2.5</v>
-      </c>
-      <c r="P4">
-        <v>5</v>
-      </c>
-      <c r="Q4">
-        <v>63.6</v>
-      </c>
       <c r="R4">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="S4">
-        <v>29.1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2954,16 +2942,16 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>91.7</v>
+        <v>92.2</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3010,19 +2998,19 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3072,16 +3060,16 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>96.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>83.59999999999999</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3134,13 +3122,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>98.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3190,7 +3178,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3199,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3249,16 +3237,16 @@
         <v>95</v>
       </c>
       <c r="P10">
+        <v>92.2</v>
+      </c>
+      <c r="Q10">
+        <v>93.8</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
         <v>90</v>
-      </c>
-      <c r="Q10">
-        <v>100</v>
-      </c>
-      <c r="R10">
-        <v>100</v>
-      </c>
-      <c r="S10">
-        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3317,7 +3305,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>98.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3370,13 +3358,13 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>87.3</v>
+        <v>85</v>
       </c>
       <c r="R12">
         <v>100</v>
       </c>
       <c r="S12">
-        <v>90.90000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3429,13 +3417,13 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>92.7</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3485,7 +3473,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3494,7 +3482,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3541,19 +3529,19 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="P15">
         <v>96.7</v>
       </c>
       <c r="Q15">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3603,7 +3591,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3612,7 +3600,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3662,7 +3650,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -3671,7 +3659,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3721,7 +3709,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3730,7 +3718,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3780,7 +3768,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>98.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -3789,7 +3777,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>94.5</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3848,7 +3836,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3898,16 +3886,16 @@
         <v>100</v>
       </c>
       <c r="P21">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="Q21">
+        <v>96.3</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
         <v>95</v>
-      </c>
-      <c r="Q21">
-        <v>100</v>
-      </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
-      <c r="S21">
-        <v>92.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3957,7 +3945,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>93.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -3966,7 +3954,7 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4025,7 +4013,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4137,13 +4125,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4193,16 +4181,16 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>98.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>85.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4249,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="P27">
         <v>96.7</v>
@@ -4261,7 +4249,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4320,7 +4308,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4367,19 +4355,19 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="P29">
-        <v>98.3</v>
+        <v>92.2</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>85.5</v>
+        <v>81.3</v>
       </c>
     </row>
   </sheetData>
@@ -4445,19 +4433,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4477,19 +4465,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>69.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4500,7 +4488,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -4509,19 +4497,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>73.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="G4" s="2">
-        <v>26.9</v>
+        <v>7.7</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4532,7 +4520,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4541,19 +4529,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>84.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="G5" s="2">
-        <v>15.4</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4573,19 +4561,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="G6" s="2">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4596,7 +4584,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -4617,7 +4605,7 @@
         <v>3.8</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4667,7 +4655,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4699,22 +4687,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920200</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4722,22 +4710,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920200</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4745,16 +4733,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920214</v>
+        <v>20330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4768,16 +4756,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920214</v>
+        <v>20330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4791,22 +4779,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920217</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4814,22 +4802,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920217</v>
+        <v>20330051920210</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4837,116 +4825,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920259</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920259</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920192</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920202</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920218</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
